--- a/public/templates/office/EMP_TST_050_AI골든셋_품질평가보고서.xlsx
+++ b/public/templates/office/EMP_TST_050_AI골든셋_품질평가보고서.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 AI 기반 화장품 표시광고 심의 및 리스크 예방 시스템 구축</t>
+          <t>한빛글로벌 엔터프라이즈 AI 콘텐츠·규제 심의 자동화 시스템(SyncGuard AI) 구축</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>(주)아모레퍼시픽 (HANBIT GLOBAL)</t>
+          <t>㈜한빛글로벌 (Hanbit Global Corp.)</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>㈜그로브소프트 (EMPASY)</t>
+          <t>㈜엠파시 (Empasy Inc.)</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>화장품법 제13조 (진피 침투, 세포 재생)</t>
+          <t>표시·광고 공정화법 제3조 (진피 침투, 세포 재생)</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조 (시술 비교, 절대효능)</t>
+          <t>표시·광고 공정화법 제3조 (시술 비교, 절대효능)</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #11 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #11 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #12 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #12 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #13 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #13 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #14 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #14 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #15 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #15 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #16 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #16 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #17 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #17 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #18 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #18 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #19 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #19 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #20 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #20 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #21 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #21 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #22 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #22 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #23 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #23 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #24 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #24 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #25 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #25 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #26 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #26 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #27 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #27 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #28 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #28 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #29 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #29 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #30 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #30 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #31 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #31 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #32 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #32 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #33 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #33 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #34 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #34 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #35 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #35 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #36 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #36 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E40" s="10" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #37 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #37 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #38 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #38 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #39 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #39 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #40 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #40 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #41 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #41 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #42 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #42 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #43 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #43 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #44 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #44 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E48" s="10" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #45 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #45 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #46 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #46 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E50" s="10" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #47 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #47 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #48 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #48 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #49 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #49 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>골든셋 표준 검증 소구 문장 샘플 #50 (아모레퍼시픽 표준 텍스트셋)</t>
+          <t>골든셋 표준 검증 소구 문장 샘플 #50 (한빛글로벌 표준 텍스트셋)</t>
         </is>
       </c>
       <c r="E54" s="10" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 가이드라인 기준</t>
+          <t>식약처 제품 표시·광고 가이드라인 기준</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr">
